--- a/docs/Mapping_casi_uso/trascrizioni/Trascr_UnCiv_999.xlsx
+++ b/docs/Mapping_casi_uso/trascrizioni/Trascr_UnCiv_999.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="686" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="707" uniqueCount="158">
   <si>
     <t>Sezione</t>
   </si>
@@ -119,6 +119,12 @@
     <t>descrizioneMotivoRecupero</t>
   </si>
   <si>
+    <t>Identificativo Atto Cartaceo</t>
+  </si>
+  <si>
+    <t>idAttoCartaceo</t>
+  </si>
+  <si>
     <t>Data unione civile</t>
   </si>
   <si>
@@ -357,6 +363,12 @@
   </si>
   <si>
     <t>nomeComuneAIRE</t>
+  </si>
+  <si>
+    <t>Residenza al momento dell'evento originario</t>
+  </si>
+  <si>
+    <t>residenzaOriginaria</t>
   </si>
   <si>
     <t>Unito civilmente 2</t>
@@ -532,11 +544,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H98"/>
+  <dimension ref="A1:H101"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="23.58203125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="33.30859375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="40.984375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="12.5625" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="49.7578125" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="30.0546875" customWidth="true" bestFit="true"/>
@@ -828,13 +840,13 @@
         <v>35</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>36</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>37</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>10</v>
@@ -848,16 +860,16 @@
         <v>23</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D14" s="2" t="s">
+      <c r="E14" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>40</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>10</v>
@@ -871,13 +883,13 @@
         <v>23</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>41</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>39</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>42</v>
@@ -897,10 +909,10 @@
         <v>43</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>44</v>
@@ -923,7 +935,7 @@
         <v>25</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>46</v>
@@ -946,7 +958,7 @@
         <v>25</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>48</v>
@@ -969,7 +981,7 @@
         <v>25</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>50</v>
@@ -992,10 +1004,10 @@
         <v>25</v>
       </c>
       <c r="D20" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>52</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>53</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>10</v>
@@ -1006,19 +1018,19 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D21" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="E21" s="2" t="s">
         <v>55</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>57</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>10</v>
@@ -1029,16 +1041,16 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>59</v>
@@ -1052,16 +1064,16 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>60</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>61</v>
@@ -1075,7 +1087,7 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>62</v>
@@ -1084,7 +1096,7 @@
         <v>25</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>63</v>
@@ -1098,16 +1110,16 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>64</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>65</v>
@@ -1121,7 +1133,7 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>66</v>
@@ -1130,7 +1142,7 @@
         <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>67</v>
@@ -1144,7 +1156,7 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>68</v>
@@ -1153,7 +1165,7 @@
         <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>69</v>
@@ -1167,16 +1179,16 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>70</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>71</v>
@@ -1190,7 +1202,7 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>72</v>
@@ -1199,7 +1211,7 @@
         <v>25</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>73</v>
@@ -1213,7 +1225,7 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>74</v>
@@ -1222,7 +1234,7 @@
         <v>25</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>75</v>
@@ -1236,7 +1248,7 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>76</v>
@@ -1245,7 +1257,7 @@
         <v>25</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>77</v>
@@ -1259,19 +1271,19 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>51</v>
+        <v>78</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>10</v>
@@ -1282,16 +1294,16 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>79</v>
+        <v>53</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>80</v>
@@ -1305,7 +1317,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>81</v>
@@ -1314,7 +1326,7 @@
         <v>25</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>82</v>
@@ -1328,7 +1340,7 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>83</v>
@@ -1337,7 +1349,7 @@
         <v>25</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>84</v>
@@ -1351,7 +1363,7 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>85</v>
@@ -1360,7 +1372,7 @@
         <v>25</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>86</v>
@@ -1374,7 +1386,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>87</v>
@@ -1383,7 +1395,7 @@
         <v>25</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>88</v>
@@ -1397,7 +1409,7 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>89</v>
@@ -1406,7 +1418,7 @@
         <v>25</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>90</v>
@@ -1420,7 +1432,7 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>91</v>
@@ -1429,7 +1441,7 @@
         <v>25</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>92</v>
@@ -1443,7 +1455,7 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>93</v>
@@ -1452,7 +1464,7 @@
         <v>25</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>94</v>
@@ -1466,7 +1478,7 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>95</v>
@@ -1475,7 +1487,7 @@
         <v>25</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>96</v>
@@ -1489,7 +1501,7 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>97</v>
@@ -1498,7 +1510,7 @@
         <v>25</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>98</v>
@@ -1512,7 +1524,7 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>99</v>
@@ -1521,7 +1533,7 @@
         <v>25</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>100</v>
@@ -1535,16 +1547,16 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>101</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>102</v>
@@ -1558,7 +1570,7 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>103</v>
@@ -1567,7 +1579,7 @@
         <v>9</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>104</v>
@@ -1581,16 +1593,16 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>105</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>106</v>
@@ -1604,7 +1616,7 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>107</v>
@@ -1613,7 +1625,7 @@
         <v>25</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>108</v>
@@ -1627,7 +1639,7 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>109</v>
@@ -1636,7 +1648,7 @@
         <v>25</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>110</v>
@@ -1650,7 +1662,7 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>111</v>
@@ -1659,7 +1671,7 @@
         <v>25</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>112</v>
@@ -1673,7 +1685,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>113</v>
@@ -1682,7 +1694,7 @@
         <v>25</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>114</v>
@@ -1696,19 +1708,19 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B51" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="B51" s="2" t="s">
-        <v>55</v>
-      </c>
       <c r="C51" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D51" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E51" s="2" t="s">
         <v>116</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>57</v>
       </c>
       <c r="F51" s="2" t="s">
         <v>10</v>
@@ -1719,19 +1731,19 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>115</v>
+        <v>56</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>58</v>
+        <v>117</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>116</v>
+        <v>58</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>59</v>
+        <v>118</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>10</v>
@@ -1742,19 +1754,19 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F53" s="2" t="s">
         <v>10</v>
@@ -1765,19 +1777,19 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>10</v>
@@ -1788,19 +1800,19 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>10</v>
@@ -1811,19 +1823,19 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F56" s="2" t="s">
         <v>10</v>
@@ -1834,19 +1846,19 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F57" s="2" t="s">
         <v>10</v>
@@ -1857,19 +1869,19 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F58" s="2" t="s">
         <v>10</v>
@@ -1880,19 +1892,19 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F59" s="2" t="s">
         <v>10</v>
@@ -1903,19 +1915,19 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F60" s="2" t="s">
         <v>10</v>
@@ -1926,19 +1938,19 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F61" s="2" t="s">
         <v>10</v>
@@ -1949,19 +1961,19 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F62" s="2" t="s">
         <v>10</v>
@@ -1972,19 +1984,19 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="B63" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="E63" s="2" t="s">
         <v>79</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D63" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="E63" s="2" t="s">
-        <v>80</v>
       </c>
       <c r="F63" s="2" t="s">
         <v>10</v>
@@ -1995,19 +2007,19 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>81</v>
+        <v>53</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>10</v>
@@ -2018,19 +2030,19 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F65" s="2" t="s">
         <v>10</v>
@@ -2041,19 +2053,19 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F66" s="2" t="s">
         <v>10</v>
@@ -2064,19 +2076,19 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F67" s="2" t="s">
         <v>10</v>
@@ -2087,19 +2099,19 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F68" s="2" t="s">
         <v>10</v>
@@ -2110,19 +2122,19 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F69" s="2" t="s">
         <v>10</v>
@@ -2133,19 +2145,19 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F70" s="2" t="s">
         <v>10</v>
@@ -2156,19 +2168,19 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F71" s="2" t="s">
         <v>10</v>
@@ -2179,19 +2191,19 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F72" s="2" t="s">
         <v>10</v>
@@ -2202,19 +2214,19 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F73" s="2" t="s">
         <v>10</v>
@@ -2225,19 +2237,19 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F74" s="2" t="s">
         <v>10</v>
@@ -2248,19 +2260,19 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F75" s="2" t="s">
         <v>10</v>
@@ -2271,19 +2283,19 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F76" s="2" t="s">
         <v>10</v>
@@ -2294,19 +2306,19 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F77" s="2" t="s">
         <v>10</v>
@@ -2317,19 +2329,19 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F78" s="2" t="s">
         <v>10</v>
@@ -2340,19 +2352,19 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F79" s="2" t="s">
         <v>10</v>
@@ -2363,19 +2375,19 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F80" s="2" t="s">
         <v>10</v>
@@ -2386,387 +2398,387 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="F81" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>121</v>
+        <v>16</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="F82" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>121</v>
+        <v>16</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B83" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="B83" s="2" t="s">
-        <v>124</v>
-      </c>
       <c r="C83" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="F83" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>121</v>
+        <v>16</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="F84" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F85" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F86" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>15</v>
+        <v>131</v>
       </c>
       <c r="F87" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B88" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E88" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="C88" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D88" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="E88" s="2" t="s">
-        <v>134</v>
-      </c>
       <c r="F88" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B89" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E89" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="C89" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D89" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="E89" s="2" t="s">
-        <v>18</v>
-      </c>
       <c r="F89" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>136</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>137</v>
+        <v>15</v>
       </c>
       <c r="F90" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B91" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E91" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="C91" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D91" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="E91" s="2" t="s">
-        <v>139</v>
-      </c>
       <c r="F91" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>141</v>
+        <v>18</v>
       </c>
       <c r="F92" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F93" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>144</v>
+        <v>121</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>14</v>
+        <v>123</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F94" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>16</v>
+        <v>125</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>146</v>
+        <v>121</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>148</v>
+        <v>123</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="F95" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>16</v>
+        <v>125</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B96" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="B96" s="2" t="s">
-        <v>150</v>
-      </c>
       <c r="C96" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>148</v>
+        <v>123</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="F96" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>16</v>
+        <v>125</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>148</v>
+        <v>14</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="F97" s="2" t="s">
         <v>10</v>
@@ -2777,24 +2789,93 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="B98" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="E98" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="F98" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G98" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="E99" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="F99" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G99" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="E100" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="F100" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G100" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B101" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C98" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D98" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="E98" s="2" t="s">
+      <c r="C101" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="E101" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F98" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G98" s="2" t="s">
+      <c r="F101" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G101" s="2" t="s">
         <v>16</v>
       </c>
     </row>

--- a/docs/Mapping_casi_uso/trascrizioni/Trascr_UnCiv_999.xlsx
+++ b/docs/Mapping_casi_uso/trascrizioni/Trascr_UnCiv_999.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="735" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="742" uniqueCount="164">
   <si>
     <t>Sezione</t>
   </si>
@@ -35,6 +35,18 @@
     <t>Condizioni obbligatorieta'</t>
   </si>
   <si>
+    <t>Allegati</t>
+  </si>
+  <si>
+    <t>Allegato generico</t>
+  </si>
+  <si>
+    <t>NO</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
     <t>Formula</t>
   </si>
   <si>
@@ -44,9 +56,6 @@
     <t>SI</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>Si puo' ignorare la sezione per</t>
   </si>
   <si>
@@ -87,9 +96,6 @@
   </si>
   <si>
     <t>Data decorrenza</t>
-  </si>
-  <si>
-    <t>NO</t>
   </si>
   <si>
     <t>dataDecorrenza</t>
@@ -556,7 +562,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H105"/>
+  <dimension ref="A1:H106"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="23.58203125" customWidth="true" bestFit="true"/>
@@ -615,63 +621,63 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="2" t="s">
+      <c r="G4" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>14</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>18</v>
@@ -680,90 +686,90 @@
         <v>10</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>26</v>
-      </c>
       <c r="F8" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>27</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>28</v>
@@ -772,21 +778,21 @@
         <v>10</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>30</v>
@@ -795,21 +801,21 @@
         <v>10</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>31</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>32</v>
@@ -818,21 +824,21 @@
         <v>10</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>34</v>
@@ -841,21 +847,21 @@
         <v>10</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>35</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>36</v>
@@ -864,12 +870,12 @@
         <v>10</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>37</v>
@@ -878,53 +884,53 @@
         <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="E14" s="2" t="s">
-        <v>39</v>
-      </c>
       <c r="F14" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D15" s="2" t="s">
+      <c r="E15" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E15" s="2" t="s">
-        <v>42</v>
-      </c>
       <c r="F15" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>41</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>44</v>
@@ -933,21 +939,21 @@
         <v>10</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>46</v>
@@ -956,21 +962,21 @@
         <v>10</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>47</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>48</v>
@@ -979,21 +985,21 @@
         <v>10</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>50</v>
@@ -1002,21 +1008,21 @@
         <v>10</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>51</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>52</v>
@@ -1025,67 +1031,67 @@
         <v>10</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>53</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="E21" s="2" t="s">
-        <v>55</v>
-      </c>
       <c r="F21" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D22" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="E22" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C22" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>59</v>
-      </c>
       <c r="F22" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>61</v>
@@ -1094,21 +1100,21 @@
         <v>10</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>62</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>63</v>
@@ -1117,12 +1123,12 @@
         <v>10</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>64</v>
@@ -1131,7 +1137,7 @@
         <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>65</v>
@@ -1140,21 +1146,21 @@
         <v>10</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>66</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>67</v>
@@ -1163,21 +1169,21 @@
         <v>10</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>69</v>
@@ -1186,12 +1192,12 @@
         <v>10</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>70</v>
@@ -1200,7 +1206,7 @@
         <v>9</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>71</v>
@@ -1209,21 +1215,21 @@
         <v>10</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>72</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>73</v>
@@ -1232,21 +1238,21 @@
         <v>10</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>74</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>75</v>
@@ -1255,21 +1261,21 @@
         <v>10</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>76</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>77</v>
@@ -1278,21 +1284,21 @@
         <v>10</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>78</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>79</v>
@@ -1301,21 +1307,21 @@
         <v>10</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>80</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>81</v>
@@ -1324,21 +1330,21 @@
         <v>10</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>82</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>83</v>
@@ -1347,44 +1353,44 @@
         <v>10</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>53</v>
+        <v>84</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>86</v>
@@ -1393,21 +1399,21 @@
         <v>10</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>87</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>88</v>
@@ -1416,21 +1422,21 @@
         <v>10</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>89</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>90</v>
@@ -1439,21 +1445,21 @@
         <v>10</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>91</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>92</v>
@@ -1462,21 +1468,21 @@
         <v>10</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>93</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>94</v>
@@ -1485,21 +1491,21 @@
         <v>10</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>95</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>96</v>
@@ -1508,21 +1514,21 @@
         <v>10</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>97</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>98</v>
@@ -1531,21 +1537,21 @@
         <v>10</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>99</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>100</v>
@@ -1554,21 +1560,21 @@
         <v>10</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>101</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>102</v>
@@ -1577,21 +1583,21 @@
         <v>10</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>103</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>104</v>
@@ -1600,21 +1606,21 @@
         <v>10</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>105</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>106</v>
@@ -1623,12 +1629,12 @@
         <v>10</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>107</v>
@@ -1637,7 +1643,7 @@
         <v>9</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>108</v>
@@ -1646,21 +1652,21 @@
         <v>10</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>109</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>110</v>
@@ -1669,21 +1675,21 @@
         <v>10</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>111</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>112</v>
@@ -1692,21 +1698,21 @@
         <v>10</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>113</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>114</v>
@@ -1715,21 +1721,21 @@
         <v>10</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>115</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>116</v>
@@ -1738,21 +1744,21 @@
         <v>10</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>117</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>118</v>
@@ -1761,21 +1767,21 @@
         <v>10</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>119</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>120</v>
@@ -1784,21 +1790,21 @@
         <v>10</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>121</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>122</v>
@@ -1807,44 +1813,44 @@
         <v>10</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B55" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="B55" s="2" t="s">
-        <v>57</v>
-      </c>
       <c r="C55" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D55" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E55" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="E55" s="2" t="s">
-        <v>59</v>
-      </c>
       <c r="F55" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>61</v>
@@ -1853,21 +1859,21 @@
         <v>10</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>62</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>63</v>
@@ -1876,12 +1882,12 @@
         <v>10</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>64</v>
@@ -1890,7 +1896,7 @@
         <v>9</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>65</v>
@@ -1899,21 +1905,21 @@
         <v>10</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>66</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>67</v>
@@ -1922,21 +1928,21 @@
         <v>10</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>69</v>
@@ -1945,12 +1951,12 @@
         <v>10</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>70</v>
@@ -1959,7 +1965,7 @@
         <v>9</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>71</v>
@@ -1968,21 +1974,21 @@
         <v>10</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>72</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>73</v>
@@ -1991,21 +1997,21 @@
         <v>10</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>74</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>75</v>
@@ -2014,21 +2020,21 @@
         <v>10</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>76</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>77</v>
@@ -2037,21 +2043,21 @@
         <v>10</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>78</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>79</v>
@@ -2060,21 +2066,21 @@
         <v>10</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>80</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>81</v>
@@ -2083,21 +2089,21 @@
         <v>10</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>82</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>83</v>
@@ -2106,44 +2112,44 @@
         <v>10</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>53</v>
+        <v>84</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F68" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>86</v>
@@ -2152,21 +2158,21 @@
         <v>10</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>87</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>88</v>
@@ -2175,21 +2181,21 @@
         <v>10</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>89</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>90</v>
@@ -2198,21 +2204,21 @@
         <v>10</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>91</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>92</v>
@@ -2221,21 +2227,21 @@
         <v>10</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>93</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>94</v>
@@ -2244,21 +2250,21 @@
         <v>10</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>95</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>96</v>
@@ -2267,21 +2273,21 @@
         <v>10</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>97</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>98</v>
@@ -2290,21 +2296,21 @@
         <v>10</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>99</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>100</v>
@@ -2313,21 +2319,21 @@
         <v>10</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>101</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>102</v>
@@ -2336,21 +2342,21 @@
         <v>10</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>103</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>104</v>
@@ -2359,21 +2365,21 @@
         <v>10</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>105</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>106</v>
@@ -2382,12 +2388,12 @@
         <v>10</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>107</v>
@@ -2396,7 +2402,7 @@
         <v>9</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>108</v>
@@ -2405,21 +2411,21 @@
         <v>10</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>109</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>110</v>
@@ -2428,21 +2434,21 @@
         <v>10</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>111</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>112</v>
@@ -2451,21 +2457,21 @@
         <v>10</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>113</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>114</v>
@@ -2474,21 +2480,21 @@
         <v>10</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>115</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>116</v>
@@ -2497,21 +2503,21 @@
         <v>10</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>117</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>118</v>
@@ -2520,21 +2526,21 @@
         <v>10</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>119</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>120</v>
@@ -2543,21 +2549,21 @@
         <v>10</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>121</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>122</v>
@@ -2566,7 +2572,7 @@
         <v>10</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="88">
@@ -2574,59 +2580,59 @@
         <v>125</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="F88" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>129</v>
+        <v>19</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B89" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E89" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="C89" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D89" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="E89" s="2" t="s">
+      <c r="F89" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G89" s="2" t="s">
         <v>131</v>
-      </c>
-      <c r="F89" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G89" s="2" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>132</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>133</v>
@@ -2635,21 +2641,21 @@
         <v>10</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B91" s="2" t="s">
         <v>134</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>135</v>
@@ -2658,21 +2664,21 @@
         <v>10</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>136</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>137</v>
@@ -2681,21 +2687,21 @@
         <v>10</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>138</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>139</v>
@@ -2704,113 +2710,113 @@
         <v>10</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>140</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>15</v>
+        <v>141</v>
       </c>
       <c r="F94" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>142</v>
+        <v>18</v>
       </c>
       <c r="F95" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B96" s="2" t="s">
         <v>143</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>18</v>
+        <v>144</v>
       </c>
       <c r="F96" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>145</v>
+        <v>21</v>
       </c>
       <c r="F97" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B98" s="2" t="s">
         <v>146</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>147</v>
@@ -2819,21 +2825,21 @@
         <v>10</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B99" s="2" t="s">
         <v>148</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E99" s="2" t="s">
         <v>149</v>
@@ -2842,21 +2848,21 @@
         <v>10</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>150</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E100" s="2" t="s">
         <v>151</v>
@@ -2865,12 +2871,12 @@
         <v>10</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>152</v>
+        <v>127</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>152</v>
@@ -2879,7 +2885,7 @@
         <v>9</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>14</v>
+        <v>129</v>
       </c>
       <c r="E101" s="2" t="s">
         <v>153</v>
@@ -2888,7 +2894,7 @@
         <v>10</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>16</v>
+        <v>131</v>
       </c>
     </row>
     <row r="102">
@@ -2896,36 +2902,36 @@
         <v>154</v>
       </c>
       <c r="B102" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E102" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="C102" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D102" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="E102" s="2" t="s">
-        <v>157</v>
-      </c>
       <c r="F102" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B103" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D103" s="2" t="s">
         <v>158</v>
-      </c>
-      <c r="C103" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D103" s="2" t="s">
-        <v>156</v>
       </c>
       <c r="E103" s="2" t="s">
         <v>159</v>
@@ -2934,21 +2940,21 @@
         <v>10</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B104" s="2" t="s">
         <v>160</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>161</v>
@@ -2957,30 +2963,53 @@
         <v>10</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>24</v>
+        <v>162</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D105" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="E105" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="F105" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G105" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="E105" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F105" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G105" s="2" t="s">
-        <v>16</v>
+      <c r="B106" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="E106" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F106" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G106" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
